--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_VALENCIA BASKET.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>53.022</v>
+        <v>66.35210000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>49.1481</v>
+        <v>46.2568</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8736</v>
+        <v>20.0955</v>
       </c>
       <c r="G2" t="n">
-        <v>18.8832</v>
+        <v>52.9009</v>
       </c>
       <c r="H2" t="n">
-        <v>19.7929</v>
+        <v>7.374599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9097999999999991</v>
+        <v>45.5261</v>
       </c>
       <c r="J2" t="n">
-        <v>53.3543</v>
+        <v>74.75060000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>37.0832</v>
+        <v>23.2922</v>
       </c>
       <c r="L2" t="n">
-        <v>16.2709</v>
+        <v>51.458</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.4714</v>
+        <v>-21.8498</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.2903</v>
+        <v>-15.9181</v>
       </c>
       <c r="O2" t="n">
-        <v>-17.181</v>
+        <v>-5.932399999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5717</v>
+        <v>7.4226</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33.4016</v>
+        <v>-48.4786</v>
       </c>
       <c r="R2" t="n">
-        <v>54.9728</v>
+        <v>55.9011</v>
       </c>
       <c r="S2" t="n">
-        <v>13.6261</v>
+        <v>5.9491</v>
       </c>
       <c r="T2" t="n">
-        <v>9.2218</v>
+        <v>2.3726</v>
       </c>
       <c r="U2" t="n">
-        <v>4.4043</v>
+        <v>3.5771</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.058600000000001</v>
+        <v>0.07959999999999959</v>
       </c>
       <c r="W2" t="n">
-        <v>19.9737</v>
+        <v>17.6117</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.0323</v>
+        <v>-17.5321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>52.8078</v>
+        <v>56.213</v>
       </c>
       <c r="E3" t="n">
-        <v>43.4539</v>
+        <v>45.4889</v>
       </c>
       <c r="F3" t="n">
-        <v>9.353299999999999</v>
+        <v>10.724</v>
       </c>
       <c r="G3" t="n">
-        <v>52.9009</v>
+        <v>5.576499999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>7.374599999999999</v>
+        <v>-1.9214</v>
       </c>
       <c r="I3" t="n">
-        <v>45.5261</v>
+        <v>7.498099999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>74.75060000000001</v>
+        <v>34.2843</v>
       </c>
       <c r="K3" t="n">
-        <v>23.2922</v>
+        <v>13.0177</v>
       </c>
       <c r="L3" t="n">
-        <v>51.458</v>
+        <v>21.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>-21.8498</v>
+        <v>-28.7073</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.9181</v>
+        <v>-14.939</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.932399999999999</v>
+        <v>-13.768</v>
       </c>
       <c r="P3" t="n">
-        <v>7.4226</v>
+        <v>5.567</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.4786</v>
+        <v>-47.5505</v>
       </c>
       <c r="R3" t="n">
-        <v>55.9011</v>
+        <v>53.1172</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.5956</v>
+        <v>5.7302</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4309000000000004</v>
+        <v>5.4458</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.1645</v>
+        <v>0.2844000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07959999999999959</v>
+        <v>39.3393</v>
       </c>
       <c r="W3" t="n">
-        <v>17.6117</v>
+        <v>53.309</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.5321</v>
+        <v>-13.9697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>42.7351</v>
+        <v>49.6374</v>
       </c>
       <c r="E4" t="n">
-        <v>35.9387</v>
+        <v>42.5267</v>
       </c>
       <c r="F4" t="n">
-        <v>6.7964</v>
+        <v>7.110800000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>5.576499999999999</v>
+        <v>18.8832</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9214</v>
+        <v>19.7929</v>
       </c>
       <c r="I4" t="n">
-        <v>7.498099999999999</v>
+        <v>-0.9097999999999991</v>
       </c>
       <c r="J4" t="n">
-        <v>34.2843</v>
+        <v>53.3543</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0177</v>
+        <v>37.0832</v>
       </c>
       <c r="L4" t="n">
-        <v>21.2661</v>
+        <v>16.2709</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.7073</v>
+        <v>-34.4714</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.939</v>
+        <v>-17.2903</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.768</v>
+        <v>-17.181</v>
       </c>
       <c r="P4" t="n">
-        <v>5.567</v>
+        <v>21.5717</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.5505</v>
+        <v>-33.4016</v>
       </c>
       <c r="R4" t="n">
-        <v>53.1172</v>
+        <v>54.9728</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.7475</v>
+        <v>10.2415</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.104200000000001</v>
+        <v>2.6003</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6431</v>
+        <v>7.6415</v>
       </c>
       <c r="V4" t="n">
-        <v>39.3393</v>
+        <v>-1.058600000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>53.309</v>
+        <v>19.9737</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.9697</v>
+        <v>-21.0323</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>36.1506</v>
+        <v>42.3683</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5556</v>
+        <v>28.37</v>
       </c>
       <c r="F5" t="n">
-        <v>13.5954</v>
+        <v>13.9985</v>
       </c>
       <c r="G5" t="n">
         <v>25.176</v>
@@ -844,13 +844,13 @@
         <v>61.6996</v>
       </c>
       <c r="S5" t="n">
-        <v>6.8843</v>
+        <v>13.1018</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.1772</v>
+        <v>1.6374</v>
       </c>
       <c r="U5" t="n">
-        <v>11.0616</v>
+        <v>11.4644</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2451</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>25.6994</v>
+        <v>24.4005</v>
       </c>
       <c r="E6" t="n">
-        <v>20.2819</v>
+        <v>7.418099999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4173</v>
+        <v>16.9824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6377000000000008</v>
+        <v>18.1783</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.878399999999999</v>
+        <v>9.198700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5157</v>
+        <v>8.979900000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>19.8667</v>
+        <v>25.3409</v>
       </c>
       <c r="K6" t="n">
-        <v>8.052399999999999</v>
+        <v>14.9723</v>
       </c>
       <c r="L6" t="n">
-        <v>11.8141</v>
+        <v>10.3692</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.2291</v>
+        <v>-7.1627</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.9309</v>
+        <v>-5.774100000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.2987</v>
+        <v>-1.388599999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.392</v>
+        <v>14.6132</v>
       </c>
       <c r="Q6" t="n">
-        <v>-35.4891</v>
+        <v>-28.7624</v>
       </c>
       <c r="R6" t="n">
-        <v>36.8812</v>
+        <v>43.3756</v>
       </c>
       <c r="S6" t="n">
-        <v>40.5287</v>
+        <v>12.0298</v>
       </c>
       <c r="T6" t="n">
-        <v>33.7635</v>
+        <v>6.6162</v>
       </c>
       <c r="U6" t="n">
-        <v>6.7647</v>
+        <v>5.4132</v>
       </c>
       <c r="V6" t="n">
-        <v>-16.8581</v>
+        <v>-20.4203</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1403</v>
+        <v>4.2229</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.9986</v>
+        <v>-24.6432</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>25.1211</v>
+        <v>13.0533</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0187</v>
+        <v>7.8934</v>
       </c>
       <c r="F7" t="n">
-        <v>19.1026</v>
+        <v>5.159599999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>18.1783</v>
+        <v>-3.178599999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>9.198700000000001</v>
+        <v>-8.552099999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>8.979900000000001</v>
+        <v>5.3733</v>
       </c>
       <c r="J7" t="n">
-        <v>25.3409</v>
+        <v>15.5334</v>
       </c>
       <c r="K7" t="n">
-        <v>14.9723</v>
+        <v>3.3639</v>
       </c>
       <c r="L7" t="n">
-        <v>10.3692</v>
+        <v>12.1695</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.1627</v>
+        <v>-18.7122</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.774100000000001</v>
+        <v>-11.9164</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.388599999999999</v>
+        <v>-6.7959</v>
       </c>
       <c r="P7" t="n">
-        <v>14.6132</v>
+        <v>20.6441</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.7624</v>
+        <v>-19.4845</v>
       </c>
       <c r="R7" t="n">
-        <v>43.3756</v>
+        <v>40.1281</v>
       </c>
       <c r="S7" t="n">
-        <v>12.7502</v>
+        <v>6.3103</v>
       </c>
       <c r="T7" t="n">
-        <v>5.216799999999999</v>
+        <v>4.418</v>
       </c>
       <c r="U7" t="n">
-        <v>7.5334</v>
+        <v>1.8927</v>
       </c>
       <c r="V7" t="n">
-        <v>-20.4203</v>
+        <v>-10.722</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2229</v>
+        <v>7.425800000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.6432</v>
+        <v>-18.1478</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>13.0413</v>
+        <v>7.015000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>8.549199999999999</v>
+        <v>2.816400000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4922</v>
+        <v>4.1988</v>
       </c>
       <c r="G8" t="n">
         <v>8.693000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>58.9162</v>
       </c>
       <c r="S8" t="n">
-        <v>21.1391</v>
+        <v>15.1132</v>
       </c>
       <c r="T8" t="n">
-        <v>12.7959</v>
+        <v>7.062799999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>8.344100000000001</v>
+        <v>8.050699999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-13.5443</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>6.386000000000001</v>
+        <v>6.294800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.415500000000002</v>
+        <v>-0.8268000000000013</v>
       </c>
       <c r="F9" t="n">
-        <v>2.970200000000001</v>
+        <v>7.1214</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.178599999999999</v>
+        <v>8.923499999999997</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.552099999999999</v>
+        <v>2.399299999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3733</v>
+        <v>6.524400000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>15.5334</v>
+        <v>41.56789999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3639</v>
+        <v>19.7557</v>
       </c>
       <c r="L9" t="n">
-        <v>12.1695</v>
+        <v>21.8115</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.7122</v>
+        <v>-32.6439</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.9164</v>
+        <v>-17.3568</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.7959</v>
+        <v>-15.2874</v>
       </c>
       <c r="P9" t="n">
-        <v>20.6441</v>
+        <v>-11.8294</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.4845</v>
+        <v>-68.8901</v>
       </c>
       <c r="R9" t="n">
-        <v>40.1281</v>
+        <v>57.0606</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3568999999999996</v>
+        <v>11.5039</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06000000000000016</v>
+        <v>6.5037</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2974999999999999</v>
+        <v>5.0003</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.722</v>
+        <v>-2.3037</v>
       </c>
       <c r="W9" t="n">
-        <v>7.425800000000001</v>
+        <v>19.9911</v>
       </c>
       <c r="X9" t="n">
-        <v>-18.1478</v>
+        <v>-22.2948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. IROEGBU</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1032</v>
+        <v>3.531999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8242000000000003</v>
+        <v>-0.1078999999999992</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.279</v>
+        <v>3.6401</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5777000000000001</v>
+        <v>0.6377000000000008</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2927</v>
+        <v>-3.878399999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8704</v>
+        <v>4.5157</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1721</v>
+        <v>19.8667</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6485</v>
+        <v>8.052399999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>2.8205</v>
+        <v>11.8141</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5944</v>
+        <v>-19.2291</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6443</v>
+        <v>-11.9309</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9501999999999999</v>
+        <v>-7.2987</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8556</v>
+        <v>1.392</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7113</v>
+        <v>-35.4891</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>36.8812</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3614</v>
+        <v>18.3609</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.499</v>
+        <v>13.3732</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8623</v>
+        <v>4.9875</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>-16.8581</v>
       </c>
       <c r="W10" t="n">
-        <v>1.214</v>
+        <v>2.1403</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6779000000000001</v>
+        <v>-18.9986</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>I. IROEGBU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8206</v>
+        <v>-0.3614000000000006</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8009</v>
+        <v>0.5479999999999996</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9803000000000002</v>
+        <v>-0.9094</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8544</v>
+        <v>0.5777000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1979</v>
+        <v>-1.2927</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6564</v>
+        <v>1.8704</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0455</v>
+        <v>2.1721</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3432</v>
+        <v>-0.6485</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3886</v>
+        <v>2.8205</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8087</v>
+        <v>-1.5944</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5408000000000001</v>
+        <v>-0.6443</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2676</v>
+        <v>-0.9501999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>1.624</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5516</v>
+        <v>-3.7113</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1756</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9801</v>
+        <v>0.3804999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2040000000000001</v>
+        <v>0.8731</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1838</v>
+        <v>-0.4927</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5698</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5698</v>
+        <v>-0.6779000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3851</v>
+        <v>-1.4911</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7494</v>
+        <v>-5.6315</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6357</v>
+        <v>4.140499999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.7436</v>
+        <v>13.0268</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9456</v>
+        <v>9.975099999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.798</v>
+        <v>3.051700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7484</v>
+        <v>34.2184</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.586</v>
+        <v>18.3647</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.1624</v>
+        <v>15.8532</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9952</v>
+        <v>-21.1914</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3596</v>
+        <v>-8.3901</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6355999999999999</v>
+        <v>-12.8014</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0876</v>
+        <v>-17.8601</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-64.7148</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>46.8545</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8069999999999999</v>
+        <v>6.0543</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9990000000000001</v>
+        <v>1.7503</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1919</v>
+        <v>4.3038</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5361</v>
+        <v>-2.711599999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>23.1145</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5361</v>
+        <v>-25.8261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0929</v>
+        <v>-2.2858</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3711</v>
+        <v>-3.2112</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.722</v>
+        <v>0.9254000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8429</v>
+        <v>-2.8544</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5318</v>
+        <v>-0.1979</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3110000000000001</v>
+        <v>-2.6564</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2486</v>
+        <v>-1.0455</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1049</v>
+        <v>0.3432</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8563999999999999</v>
+        <v>-1.3886</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5943</v>
+        <v>-1.8087</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4267000000000001</v>
+        <v>-0.5408000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1674</v>
+        <v>-1.2676</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4639</v>
+        <v>1.624</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.6391</v>
+        <v>-2.5516</v>
       </c>
       <c r="R13" t="n">
-        <v>4.1753</v>
+        <v>4.1756</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8969</v>
+        <v>1.5145</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9494</v>
+        <v>0.3857999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0526</v>
+        <v>1.1288</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6831</v>
+        <v>-2.5698</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5672</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.2503</v>
+        <v>-2.5698</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.355900000000002</v>
+        <v>-4.4442</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.7149</v>
+        <v>-3.4388</v>
       </c>
       <c r="F14" t="n">
-        <v>1.359</v>
+        <v>-1.0054</v>
       </c>
       <c r="G14" t="n">
-        <v>8.923499999999997</v>
+        <v>-6.7436</v>
       </c>
       <c r="H14" t="n">
-        <v>2.399299999999999</v>
+        <v>-2.9456</v>
       </c>
       <c r="I14" t="n">
-        <v>6.524400000000002</v>
+        <v>-3.798</v>
       </c>
       <c r="J14" t="n">
-        <v>41.56789999999999</v>
+        <v>-4.7484</v>
       </c>
       <c r="K14" t="n">
-        <v>19.7557</v>
+        <v>-1.586</v>
       </c>
       <c r="L14" t="n">
-        <v>21.8115</v>
+        <v>-3.1624</v>
       </c>
       <c r="M14" t="n">
-        <v>-32.6439</v>
+        <v>-1.9952</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.3568</v>
+        <v>-1.3596</v>
       </c>
       <c r="O14" t="n">
-        <v>-15.2874</v>
+        <v>-0.6355999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-11.8294</v>
+        <v>2.0876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-68.8901</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>57.0606</v>
+        <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1465</v>
+        <v>0.748</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3842000000000003</v>
+        <v>1.3095</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7622000000000002</v>
+        <v>-0.5616</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3037</v>
+        <v>-0.5361</v>
       </c>
       <c r="W14" t="n">
-        <v>19.9911</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.2948</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.6573</v>
+        <v>-6.109</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.8487</v>
+        <v>-2.9476</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8087</v>
+        <v>-3.1613</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.363899999999999</v>
+        <v>-1.8429</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.8805</v>
+        <v>-1.5318</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.4832</v>
+        <v>-0.3110000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.876</v>
+        <v>-0.2486</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0412</v>
+        <v>-1.1049</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.8347</v>
+        <v>0.8563999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.4878</v>
+        <v>-1.5943</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.8391</v>
+        <v>-0.4267000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6486999999999999</v>
+        <v>-1.1674</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3918</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.958699999999999</v>
+        <v>-4.6391</v>
       </c>
       <c r="R15" t="n">
-        <v>8.3505</v>
+        <v>4.1753</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.8654</v>
+        <v>0.8807</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7641</v>
+        <v>1.3727</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1013</v>
+        <v>-0.4919</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8197000000000001</v>
+        <v>-4.6831</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7501</v>
+        <v>0.5672</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5698</v>
+        <v>-5.2503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-19.6621</v>
+        <v>-9.2408</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.4554</v>
+        <v>-9.0046</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.207000000000001</v>
+        <v>-0.2361</v>
       </c>
       <c r="G16" t="n">
-        <v>13.0268</v>
+        <v>-9.363899999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>9.975099999999999</v>
+        <v>-5.8805</v>
       </c>
       <c r="I16" t="n">
-        <v>3.051700000000001</v>
+        <v>-3.4832</v>
       </c>
       <c r="J16" t="n">
-        <v>34.2184</v>
+        <v>-3.876</v>
       </c>
       <c r="K16" t="n">
-        <v>18.3647</v>
+        <v>-1.0412</v>
       </c>
       <c r="L16" t="n">
-        <v>15.8532</v>
+        <v>-2.8347</v>
       </c>
       <c r="M16" t="n">
-        <v>-21.1914</v>
+        <v>-5.4878</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.3901</v>
+        <v>-4.8391</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.8014</v>
+        <v>-0.6486999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.8601</v>
+        <v>1.3918</v>
       </c>
       <c r="Q16" t="n">
-        <v>-64.7148</v>
+        <v>-6.958699999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>46.8545</v>
+        <v>8.3505</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.1172</v>
+        <v>-0.4491000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.073499999999999</v>
+        <v>0.07980000000000009</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.0436</v>
+        <v>-0.5286</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.711599999999999</v>
+        <v>-0.8197000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>23.1145</v>
+        <v>1.7501</v>
       </c>
       <c r="X16" t="n">
-        <v>-25.8261</v>
+        <v>-2.5698</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.2476</v>
+        <v>-18.7697</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.985</v>
+        <v>-13.0653</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.262599999999999</v>
+        <v>-5.704800000000001</v>
       </c>
       <c r="G17" t="n">
         <v>6.6434</v>
@@ -1780,13 +1780,13 @@
         <v>20.6441</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.8919</v>
+        <v>-0.4134999999999998</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3136</v>
+        <v>-0.3940000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.5781</v>
+        <v>-0.01969999999999994</v>
       </c>
       <c r="V17" t="n">
         <v>-6.9071</v>
@@ -1813,13 +1813,13 @@
         <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>-25.2066</v>
+        <v>-23.9472</v>
       </c>
       <c r="E18" t="n">
-        <v>-20.5579</v>
+        <v>-19.8422</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.648899999999999</v>
+        <v>-4.104399999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-8.4969</v>
@@ -1858,13 +1858,13 @@
         <v>34.3293</v>
       </c>
       <c r="S18" t="n">
-        <v>9.314399999999999</v>
+        <v>10.5738</v>
       </c>
       <c r="T18" t="n">
-        <v>4.185599999999999</v>
+        <v>4.9008</v>
       </c>
       <c r="U18" t="n">
-        <v>5.1286</v>
+        <v>5.6728</v>
       </c>
       <c r="V18" t="n">
         <v>-25.56</v>
@@ -1891,19 +1891,19 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>154.432</v>
+        <v>202.2172</v>
       </c>
       <c r="E19" t="n">
-        <v>110.0541</v>
+        <v>123.2424</v>
       </c>
       <c r="F19" t="n">
-        <v>44.3764</v>
+        <v>78.97560000000001</v>
       </c>
       <c r="G19" t="n">
         <v>126.7367</v>
       </c>
       <c r="H19" t="n">
-        <v>43.19530000000001</v>
+        <v>43.1953</v>
       </c>
       <c r="I19" t="n">
         <v>83.5421</v>
@@ -1936,16 +1936,16 @@
         <v>584.5249</v>
       </c>
       <c r="S19" t="n">
-        <v>69.84439999999999</v>
+        <v>117.6299</v>
       </c>
       <c r="T19" t="n">
-        <v>47.1213</v>
+        <v>60.30800000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>22.7234</v>
+        <v>57.3227</v>
       </c>
       <c r="V19" t="n">
-        <v>-69.9845</v>
+        <v>-69.98450000000001</v>
       </c>
       <c r="W19" t="n">
         <v>203.9787</v>
